--- a/diseases/d208/2000-2004.xlsx
+++ b/diseases/d208/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>75</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>1.448938956491551</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>59</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.31377749552592</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>50</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.9659593043277006</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>57</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>1.269242665169109</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>51</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.9852784904142545</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>40</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.8906966071362167</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>44</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.8500441878083765</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>45</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.002033683028244</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>45</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.8693633738949305</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>44</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.9797662678498383</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>42</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.8114058156352685</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>54</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.202440419633892</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>33</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.6375331408562824</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>27</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.6012202098169462</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>39</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.7534482573756064</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>38</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.8461617767794058</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>34</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.6568523269428364</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>45</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.002033683028244</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>39</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.7534482573756064</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>59</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.31377749552592</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>27</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.5216180243369583</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>49</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.091103343741865</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>26</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.5022988382504042</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>32</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.7125572857089734</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>37</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.7131882579914189</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>43</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.9526643251802251</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>16</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.3084057331854785</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>50</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>1.107749215325843</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>28</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.5397100330745873</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>52</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.152059183938877</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>31</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.5975361080468645</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>37</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.8197344193411241</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>36</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.6939128996673266</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>36</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.7975794350346073</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>37</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.7131882579914189</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>36</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.7975794350346073</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>20</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.3855071664818481</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>32</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.7089594978085397</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>31</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.5975361080468645</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>38</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.8418894036476409</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>23</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.4433332414541253</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>47</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.041284262406293</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>24</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.4626085997782177</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>64</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.417918995617079</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>39</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.7517389746396038</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>56</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.240679121164945</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>22</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.424057883130033</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>35</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.7754244507280903</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>19</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3653462540279425</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>72</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>1.58659713257826</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>16</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.3076600033919515</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>39</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.8594067801465575</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>27</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.5191762557239182</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>50</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.101803564290458</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>29</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.5576337561479121</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>63</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>1.388272491005978</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>36</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.6922350076318909</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>54</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>1.189947849433695</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>26</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.4999475055119212</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>64</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>1.410308562291787</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>26</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.4999475055119212</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>40</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.8814428514323667</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>36</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.6922350076318909</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>53</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.167911778147886</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>21</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.4038037544519364</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>67</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>1.476416776149214</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>27</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.5191762557239182</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>76</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>1.674741417721497</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>19</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.3653462540279425</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>89</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.961210344437016</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>15</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>39</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.8594067801465575</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>29</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.556306355991947</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>60</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.314443610259583</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>22</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.4220255114421667</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>63</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>1.380165790772562</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>21</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.4028425336493409</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>53</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>1.161091855729298</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>32</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.6138552893704243</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>89</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>1.949758021885048</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>19</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.3644765780636894</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>75</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>1.643054512824479</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>20</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.3836595558565151</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>58</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.27062882325093</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>20</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.3836595558565151</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>38</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.8324809531644025</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>21</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.4028425336493409</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>44</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.9639253141903609</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>29</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.556306355991947</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>90</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>1.971665415389374</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>24</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.4603914670278182</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>96</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>2.103109776415332</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>24</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.4603914670278182</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>63</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.380165790772562</v>
       </c>
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>18</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.3452936002708636</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>71</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>1.555424938807173</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>21</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.4016718730992314</v>
       </c>
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>55</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.197802359343975</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>36</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.6885803538843965</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>64</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>1.39380638178208</v>
       </c>
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>27</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.5164352654132973</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>62</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>1.350249932351389</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>33</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.6311986577273635</v>
       </c>
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>46</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>1.00179833690587</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>22</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.4207991051515756</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>58</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>1.26313703349001</v>
       </c>
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>24</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.4590535692562644</v>
       </c>
@@ -43137,9 +42816,6 @@
       <c r="O216" t="n">
         <v>64</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>1.39380638178208</v>
       </c>
@@ -43533,9 +43209,6 @@
       <c r="O218" t="n">
         <v>27</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.5164352654132973</v>
       </c>
@@ -43929,9 +43602,6 @@
       <c r="O220" t="n">
         <v>30</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.6533467414603498</v>
       </c>
@@ -44325,9 +43995,6 @@
       <c r="O222" t="n">
         <v>27</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.5164352654132973</v>
       </c>
@@ -44721,9 +44388,6 @@
       <c r="O224" t="n">
         <v>48</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>1.04535478633656</v>
       </c>
@@ -45117,9 +44781,6 @@
       <c r="O226" t="n">
         <v>31</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.5929441936226748</v>
       </c>
@@ -45513,9 +45174,6 @@
       <c r="O228" t="n">
         <v>64</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>1.39380638178208</v>
       </c>
@@ -45909,9 +45567,6 @@
       <c r="O230" t="n">
         <v>15</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.2869084807851652</v>
       </c>
@@ -46305,9 +45960,6 @@
       <c r="O232" t="n">
         <v>76</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.655145078366219</v>
       </c>
@@ -46701,9 +46353,6 @@
       <c r="O234" t="n">
         <v>24</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.4590535692562644</v>
       </c>
@@ -47097,9 +46746,6 @@
       <c r="O236" t="n">
         <v>69</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>1.502697505358805</v>
       </c>
@@ -47493,9 +47139,6 @@
       <c r="O238" t="n">
         <v>23</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.43992633720392</v>
       </c>
@@ -47888,9 +47531,6 @@
       </c>
       <c r="O240" t="n">
         <v>66</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>1.43736283121277</v>
